--- a/Figure 2/Figure 2-C.xlsx
+++ b/Figure 2/Figure 2-C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D491C476-7FA8-4983-B475-671138099D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A30B64-A458-4AFB-8E74-603465A3C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>F/G</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CON 1</t>
@@ -98,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,18 +114,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -133,8 +128,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -157,17 +163,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,171 +460,172 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="4"/>
+    <col min="2" max="2" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5">
         <v>2.1247368421052646</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="5">
         <v>1.6598000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>1.5454545454545461</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>2.8000000000000052</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>1.5265263157894717</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <v>9.000000000000032</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>5.9599999999999858</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>2.115555555555559</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>5.6183333333333527</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>2.2576666666666689</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>4.4654999999999783</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="5">
         <v>6.5831428571428638</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>3.2029999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="5">
         <v>4.3404999999999969</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="5">
         <v>3.89116666666667</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="5">
         <v>1.4712727272727277</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="5">
         <v>1.8536470588235308</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="5">
         <v>2.0851428571428596</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="5">
         <v>2.6244000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="5">
         <v>2.8987692307692292</v>
       </c>
     </row>
